--- a/opportunities/activity_tracker.xlsx
+++ b/opportunities/activity_tracker.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,11 +35,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -102,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -118,10 +113,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1287,33 +1278,8 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>How to use</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Priority 1 = do today. Priority 2 = this week / before deadline. Priority 3 = later. Done = already applied or finished. Update the Status column as you finish (To do -&gt; Doing -&gt; Done).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Built 2026-08-11 10:24 from tracker.xlsx + new_grants.xlsx. Rebuild: python opportunities/build_activity_tracker.py</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:H19"/>
-  <mergeCells count="2">
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A22:H22"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>